--- a/src/test/resources/tutorial/Default-Value-Student.xlsx
+++ b/src/test/resources/tutorial/Default-Value-Student.xlsx
@@ -123,7 +123,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="n" s="9">
-        <v>20.0</v>
+        <v>21.0</v>
       </c>
       <c r="D2" t="n" s="12">
         <v>37928.5</v>
@@ -137,7 +137,7 @@
         <v>7</v>
       </c>
       <c r="C3" t="n" s="9">
-        <v>23.0</v>
+        <v>24.0</v>
       </c>
       <c r="D3" t="n" s="12">
         <v>36615.5</v>
@@ -151,7 +151,7 @@
         <v>9</v>
       </c>
       <c r="C4" t="n" s="9">
-        <v>30.0</v>
+        <v>31.0</v>
       </c>
       <c r="D4" t="n" s="12">
         <v>34158.5</v>
